--- a/data/dividends_info_20260407.xlsx
+++ b/data/dividends_info_20260407.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>30.14999961853027</v>
+        <v>30.29999923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2985074664634017</v>
+        <v>0.2970297104493625</v>
       </c>
       <c r="J2" t="n">
         <v>342</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>52</v>
+        <v>51.65000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.346153846153846</v>
+        <v>1.355275855411678</v>
       </c>
       <c r="J3" t="n">
         <v>321</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.674157332266361</v>
       </c>
       <c r="J4" t="n">
         <v>251</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30.14999961853027</v>
+        <v>30.29999923706055</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2985074664634017</v>
+        <v>0.2970297104493625</v>
       </c>
       <c r="J5" t="n">
         <v>251</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.065000057220459</v>
+        <v>2.039999961853027</v>
       </c>
       <c r="I6" t="n">
-        <v>3.728813455997861</v>
+        <v>3.774509874503002</v>
       </c>
       <c r="J6" t="n">
         <v>230</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5.809999942779541</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="I7" t="n">
-        <v>3.442340825640675</v>
+        <v>3.436426015480821</v>
       </c>
       <c r="J7" t="n">
         <v>223</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5.599999904632568</v>
       </c>
       <c r="I8" t="n">
-        <v>1.090909090909091</v>
+        <v>1.071428589674892</v>
       </c>
       <c r="J8" t="n">
         <v>195</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>30.15500068664551</v>
+        <v>30.29999923706055</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2984579603735759</v>
+        <v>0.2970297104493625</v>
       </c>
       <c r="J9" t="n">
         <v>167</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>9.78600025177002</v>
+        <v>9.767000198364258</v>
       </c>
       <c r="I10" t="n">
-        <v>2.656856665755482</v>
+        <v>2.662025132788918</v>
       </c>
       <c r="J10" t="n">
         <v>104</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>16.68000030517578</v>
+        <v>16.39999961853027</v>
       </c>
       <c r="I11" t="n">
-        <v>3.597122236345648</v>
+        <v>3.658536670464694</v>
       </c>
       <c r="J11" t="n">
         <v>104</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="I12" t="n">
-        <v>2.088888888888889</v>
+        <v>2.032432432432433</v>
       </c>
       <c r="J12" t="n">
         <v>104</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.340000152587891</v>
+        <v>5.210000038146973</v>
       </c>
       <c r="I13" t="n">
-        <v>2.247190947023572</v>
+        <v>2.303262938989922</v>
       </c>
       <c r="J13" t="n">
         <v>97</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5494505264177207</v>
       </c>
       <c r="J14" t="n">
         <v>97</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3.900000095367432</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="I16" t="n">
-        <v>1.794871750981459</v>
+        <v>1.75879396142052</v>
       </c>
       <c r="J16" t="n">
         <v>90</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>31.35000038146973</v>
+        <v>31.14999961853027</v>
       </c>
       <c r="I17" t="n">
-        <v>0.478468893699477</v>
+        <v>0.481540936876189</v>
       </c>
       <c r="J17" t="n">
         <v>90</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6.25</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="I18" t="n">
-        <v>0.64</v>
+        <v>0.6504064939792525</v>
       </c>
       <c r="J18" t="n">
         <v>83</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>23.02000045776367</v>
+        <v>22.92000007629395</v>
       </c>
       <c r="I19" t="n">
-        <v>4.126846138613368</v>
+        <v>4.14485164414367</v>
       </c>
       <c r="J19" t="n">
         <v>76</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>23.79999923706055</v>
+        <v>23.85000038146973</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8193277573570367</v>
+        <v>0.817610049815787</v>
       </c>
       <c r="J20" t="n">
         <v>76</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.850000023841858</v>
+        <v>1.845000028610229</v>
       </c>
       <c r="I21" t="n">
-        <v>1.783783760795287</v>
+        <v>1.788617858442944</v>
       </c>
       <c r="J21" t="n">
         <v>76</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5.394999980926514</v>
+        <v>5.304999828338623</v>
       </c>
       <c r="I22" t="n">
-        <v>5.375347563026249</v>
+        <v>5.466541175946086</v>
       </c>
       <c r="J22" t="n">
         <v>76</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.116000175476074</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="I23" t="n">
-        <v>3.887269027666981</v>
+        <v>3.902439115162341</v>
       </c>
       <c r="J23" t="n">
         <v>76</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.563999891281128</v>
+        <v>2.552000045776367</v>
       </c>
       <c r="I24" t="n">
-        <v>5.405616453858238</v>
+        <v>5.431034385339724</v>
       </c>
       <c r="J24" t="n">
         <v>76</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>59.20000076293945</v>
+        <v>57.25</v>
       </c>
       <c r="I25" t="n">
-        <v>1.064189175474461</v>
+        <v>1.100436681222707</v>
       </c>
       <c r="J25" t="n">
         <v>76</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>17.25</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="I26" t="n">
-        <v>4.521739130434783</v>
+        <v>4.561403407015362</v>
       </c>
       <c r="J26" t="n">
         <v>76</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>21.01000022888184</v>
+        <v>20.95999908447266</v>
       </c>
       <c r="I27" t="n">
-        <v>4.045692483294359</v>
+        <v>4.055343688586738</v>
       </c>
       <c r="J27" t="n">
         <v>76</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>30.15500068664551</v>
+        <v>30.29999923706055</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2984579603735759</v>
+        <v>0.2970297104493625</v>
       </c>
       <c r="J28" t="n">
         <v>76</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6.677999973297119</v>
+        <v>6.711999893188477</v>
       </c>
       <c r="I29" t="n">
-        <v>2.714884706872603</v>
+        <v>2.701132343342083</v>
       </c>
       <c r="J29" t="n">
         <v>76</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>9.973999977111816</v>
+        <v>10.03999996185303</v>
       </c>
       <c r="I31" t="n">
-        <v>2.777220780385556</v>
+        <v>2.758964153908977</v>
       </c>
       <c r="J31" t="n">
         <v>76</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3.924000024795532</v>
+        <v>3.946000099182129</v>
       </c>
       <c r="I32" t="n">
-        <v>2.803261959860252</v>
+        <v>2.787632976055912</v>
       </c>
       <c r="J32" t="n">
         <v>69</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.026999950408936</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I33" t="n">
-        <v>1.184015815844403</v>
+        <v>1.090909067264274</v>
       </c>
       <c r="J33" t="n">
         <v>69</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>27.10000038146973</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="I34" t="n">
-        <v>4.095940901753599</v>
+        <v>4.172932270983183</v>
       </c>
       <c r="J34" t="n">
         <v>58</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.8899999856948853</v>
+        <v>0.8690000176429749</v>
       </c>
       <c r="I35" t="n">
-        <v>3.370786571033133</v>
+        <v>3.452243888483484</v>
       </c>
       <c r="J35" t="n">
         <v>55</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.5019999742507935</v>
+        <v>0.5</v>
       </c>
       <c r="I36" t="n">
-        <v>4.58167354178179</v>
+        <v>4.6</v>
       </c>
       <c r="J36" t="n">
         <v>55</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.630000114440918</v>
+        <v>2.589999914169312</v>
       </c>
       <c r="I37" t="n">
-        <v>6.844106166066238</v>
+        <v>6.949807180118431</v>
       </c>
       <c r="J37" t="n">
         <v>48</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>8.600000381469727</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I38" t="n">
-        <v>3.488371938289734</v>
+        <v>3.370786661331805</v>
       </c>
       <c r="J38" t="n">
         <v>48</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>12.69999980926514</v>
+        <v>12.4399995803833</v>
       </c>
       <c r="I39" t="n">
-        <v>1.968503966571837</v>
+        <v>2.00964637003868</v>
       </c>
       <c r="J39" t="n">
         <v>48</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3.420000076293945</v>
+        <v>3.359999895095825</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8771929628875695</v>
+        <v>0.8928571707334656</v>
       </c>
       <c r="J40" t="n">
         <v>48</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3.440000057220459</v>
+        <v>3.470000028610229</v>
       </c>
       <c r="I41" t="n">
-        <v>4.360465043747729</v>
+        <v>4.322766534963878</v>
       </c>
       <c r="J41" t="n">
         <v>48</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>14.10000038146973</v>
+        <v>13.75</v>
       </c>
       <c r="I42" t="n">
-        <v>4.113475066016581</v>
+        <v>4.218181818181818</v>
       </c>
       <c r="J42" t="n">
         <v>48</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2.528000116348267</v>
+        <v>2.517999887466431</v>
       </c>
       <c r="I43" t="n">
-        <v>4.11392386129434</v>
+        <v>4.130262297376155</v>
       </c>
       <c r="J43" t="n">
         <v>41</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>9.14799976348877</v>
+        <v>9.069999694824219</v>
       </c>
       <c r="I44" t="n">
-        <v>3.17009190530852</v>
+        <v>3.197354021582691</v>
       </c>
       <c r="J44" t="n">
         <v>41</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2.069999933242798</v>
+        <v>2.039999961853027</v>
       </c>
       <c r="I45" t="n">
-        <v>3.719806883248261</v>
+        <v>3.774509874503002</v>
       </c>
       <c r="J45" t="n">
         <v>41</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>35.81000137329102</v>
+        <v>35.40000152587891</v>
       </c>
       <c r="I46" t="n">
-        <v>4.579726157796794</v>
+        <v>4.632768161891435</v>
       </c>
       <c r="J46" t="n">
         <v>41</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>33.43999862670898</v>
+        <v>33.22000122070312</v>
       </c>
       <c r="I47" t="n">
-        <v>5.980861489637062</v>
+        <v>6.020469375400187</v>
       </c>
       <c r="J47" t="n">
         <v>41</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>3.818000078201294</v>
+        <v>3.799999952316284</v>
       </c>
       <c r="I48" t="n">
-        <v>2.619172287893488</v>
+        <v>2.631578980390386</v>
       </c>
       <c r="J48" t="n">
         <v>41</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>36.27999877929688</v>
+        <v>36.02999877929688</v>
       </c>
       <c r="I49" t="n">
-        <v>0.409206187969109</v>
+        <v>0.4120455315843816</v>
       </c>
       <c r="J49" t="n">
         <v>41</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>21.1200008392334</v>
+        <v>21.78000068664551</v>
       </c>
       <c r="I50" t="n">
-        <v>4.356060432966316</v>
+        <v>4.224058636343853</v>
       </c>
       <c r="J50" t="n">
         <v>41</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>8.215000152587891</v>
+        <v>8.135000228881836</v>
       </c>
       <c r="I51" t="n">
-        <v>3.651856292485812</v>
+        <v>3.687768796058599</v>
       </c>
       <c r="J51" t="n">
         <v>41</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>76.63999938964844</v>
+        <v>74.66000366210938</v>
       </c>
       <c r="I52" t="n">
-        <v>1.356993747758915</v>
+        <v>1.392981447880385</v>
       </c>
       <c r="J52" t="n">
         <v>41</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>44.77000045776367</v>
+        <v>43.52999877929688</v>
       </c>
       <c r="I53" t="n">
-        <v>1.563547002105539</v>
+        <v>1.608086422306366</v>
       </c>
       <c r="J53" t="n">
         <v>41</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>52.04999923706055</v>
+        <v>51.65000152587891</v>
       </c>
       <c r="I54" t="n">
-        <v>4.226705153212682</v>
+        <v>4.259438402722417</v>
       </c>
       <c r="J54" t="n">
         <v>41</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>7.415999889373779</v>
+        <v>7.361000061035156</v>
       </c>
       <c r="I55" t="n">
-        <v>11.59654817730344</v>
+        <v>11.68319512116755</v>
       </c>
       <c r="J55" t="n">
         <v>41</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>11.46000003814697</v>
+        <v>11.38599967956543</v>
       </c>
       <c r="I56" t="n">
-        <v>4.886561938358853</v>
+        <v>4.918320883189886</v>
       </c>
       <c r="J56" t="n">
         <v>41</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1.850000023841858</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="I57" t="n">
-        <v>2.162162134297318</v>
+        <v>2.139037427700682</v>
       </c>
       <c r="J57" t="n">
         <v>41</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>8.840000152587891</v>
+        <v>8.619999885559082</v>
       </c>
       <c r="I58" t="n">
-        <v>3.393665099792738</v>
+        <v>3.480278468478685</v>
       </c>
       <c r="J58" t="n">
         <v>41</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.279999971389771</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I59" t="n">
-        <v>4.736842164702693</v>
+        <v>4.778761082112308</v>
       </c>
       <c r="J59" t="n">
         <v>41</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>68.90000152587891</v>
+        <v>69.59999847412109</v>
       </c>
       <c r="I60" t="n">
-        <v>2.989840282117065</v>
+        <v>2.959770179831191</v>
       </c>
       <c r="J60" t="n">
         <v>41</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>14.76000022888184</v>
+        <v>14.71000003814697</v>
       </c>
       <c r="I61" t="n">
-        <v>5.081300734212911</v>
+        <v>5.098572386506111</v>
       </c>
       <c r="J61" t="n">
         <v>41</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>15.64000034332275</v>
+        <v>15.47000026702881</v>
       </c>
       <c r="I62" t="n">
-        <v>1.91815852566832</v>
+        <v>1.939237199881564</v>
       </c>
       <c r="J62" t="n">
         <v>41</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>42.70000076293945</v>
+        <v>40.79999923706055</v>
       </c>
       <c r="I63" t="n">
-        <v>1.990632282933679</v>
+        <v>2.083333372290618</v>
       </c>
       <c r="J63" t="n">
         <v>41</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>31.78000068664551</v>
+        <v>31.54000091552734</v>
       </c>
       <c r="I64" t="n">
-        <v>2.674638079404398</v>
+        <v>2.694990410040031</v>
       </c>
       <c r="J64" t="n">
         <v>41</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>61.02000045776367</v>
+        <v>59.38000106811523</v>
       </c>
       <c r="I65" t="n">
-        <v>2.130449017121564</v>
+        <v>2.189289283623893</v>
       </c>
       <c r="J65" t="n">
         <v>41</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>7.159999847412109</v>
+        <v>7.139999866485596</v>
       </c>
       <c r="I66" t="n">
-        <v>8.37988844674155</v>
+        <v>8.403361501676443</v>
       </c>
       <c r="J66" t="n">
         <v>41</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>5.150000095367432</v>
+        <v>5.349999904632568</v>
       </c>
       <c r="I67" t="n">
-        <v>9.126213423234264</v>
+        <v>8.785046885571468</v>
       </c>
       <c r="J67" t="n">
         <v>41</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>5.809999942779541</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="I68" t="n">
-        <v>3.442340825640675</v>
+        <v>3.436426015480821</v>
       </c>
       <c r="J68" t="n">
         <v>41</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>22.81999969482422</v>
+        <v>22.55999946594238</v>
       </c>
       <c r="I69" t="n">
-        <v>4.382121005140982</v>
+        <v>4.432624218407656</v>
       </c>
       <c r="J69" t="n">
         <v>41</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>7.800000190734863</v>
+        <v>7.699999809265137</v>
       </c>
       <c r="I71" t="n">
-        <v>2.564102501402085</v>
+        <v>2.597402661742239</v>
       </c>
       <c r="J71" t="n">
         <v>41</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>9.5</v>
+        <v>9.454999923706055</v>
       </c>
       <c r="I72" t="n">
-        <v>2.526315789473684</v>
+        <v>2.538339523390792</v>
       </c>
       <c r="J72" t="n">
         <v>41</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>19.35000038146973</v>
+        <v>19.40500068664551</v>
       </c>
       <c r="I73" t="n">
-        <v>4.082687258014388</v>
+        <v>4.071115547775666</v>
       </c>
       <c r="J73" t="n">
         <v>41</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>5.5</v>
+        <v>5.599999904632568</v>
       </c>
       <c r="I75" t="n">
-        <v>1.090909090909091</v>
+        <v>1.071428589674892</v>
       </c>
       <c r="J75" t="n">
         <v>41</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>34.54000091552734</v>
+        <v>34.38000106811523</v>
       </c>
       <c r="I76" t="n">
-        <v>1.013317865439484</v>
+        <v>1.018033708918635</v>
       </c>
       <c r="J76" t="n">
         <v>41</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>12.5</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>1.626016234948131</v>
       </c>
       <c r="J78" t="n">
         <v>41</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>5.78000020980835</v>
+        <v>5.664999961853027</v>
       </c>
       <c r="I79" t="n">
-        <v>1.782006855730118</v>
+        <v>1.818181830425089</v>
       </c>
       <c r="J79" t="n">
         <v>41</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>5.355000019073486</v>
+        <v>5.369999885559082</v>
       </c>
       <c r="I80" t="n">
-        <v>3.548085888389474</v>
+        <v>3.538175121957544</v>
       </c>
       <c r="J80" t="n">
         <v>41</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>25.64999961853027</v>
+        <v>25.38999938964844</v>
       </c>
       <c r="I82" t="n">
-        <v>1.715399635648071</v>
+        <v>1.732965776200015</v>
       </c>
       <c r="J82" t="n">
         <v>41</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.059999942779541</v>
+        <v>1.070000052452087</v>
       </c>
       <c r="I83" t="n">
-        <v>2.830188832023306</v>
+        <v>2.803738180315963</v>
       </c>
       <c r="J83" t="n">
         <v>41</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>7.900000095367432</v>
+        <v>7.829999923706055</v>
       </c>
       <c r="I84" t="n">
-        <v>5.949367016787867</v>
+        <v>6.002554336904029</v>
       </c>
       <c r="J84" t="n">
         <v>41</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>53</v>
+        <v>50.97999954223633</v>
       </c>
       <c r="I85" t="n">
-        <v>2.641509433962264</v>
+        <v>2.74617499523537</v>
       </c>
       <c r="J85" t="n">
         <v>41</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>3.33299994468689</v>
+        <v>3.28600001335144</v>
       </c>
       <c r="I86" t="n">
-        <v>9.000900239384274</v>
+        <v>9.129640863696331</v>
       </c>
       <c r="J86" t="n">
         <v>41</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>12.14999961853027</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9876543519967272</v>
+        <v>0.9917355059242088</v>
       </c>
       <c r="J87" t="n">
         <v>41</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>3.420000076293945</v>
+        <v>3.589999914169312</v>
       </c>
       <c r="I88" t="n">
-        <v>4.970760123029561</v>
+        <v>4.735376157782896</v>
       </c>
       <c r="J88" t="n">
         <v>41</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>22.10000038146973</v>
+        <v>21.25</v>
       </c>
       <c r="I89" t="n">
-        <v>3.167420759806555</v>
+        <v>3.294117647058823</v>
       </c>
       <c r="J89" t="n">
         <v>41</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>2.980000019073486</v>
+        <v>2.680000066757202</v>
       </c>
       <c r="I90" t="n">
-        <v>1.174496636777938</v>
+        <v>1.305970116722794</v>
       </c>
       <c r="J90" t="n">
         <v>41</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>6.130000114440918</v>
+        <v>6.170000076293945</v>
       </c>
       <c r="I91" t="n">
-        <v>5.383360421520929</v>
+        <v>5.348460225598845</v>
       </c>
       <c r="J91" t="n">
         <v>41</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0.9440000057220459</v>
+        <v>0.9390000104904175</v>
       </c>
       <c r="I92" t="n">
-        <v>7.415254192340652</v>
+        <v>7.45473900084843</v>
       </c>
       <c r="J92" t="n">
         <v>41</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>49.72000122070312</v>
+        <v>49.11999893188477</v>
       </c>
       <c r="I93" t="n">
-        <v>1.427996746919548</v>
+        <v>1.445439770844793</v>
       </c>
       <c r="J93" t="n">
         <v>41</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>82.69999694824219</v>
+        <v>80.90000152587891</v>
       </c>
       <c r="I94" t="n">
-        <v>1.6324063480255</v>
+        <v>1.668726791764215</v>
       </c>
       <c r="J94" t="n">
         <v>41</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>7.059999942779541</v>
+        <v>7</v>
       </c>
       <c r="I95" t="n">
-        <v>1.133144485104681</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="J95" t="n">
         <v>41</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>4.047999858856201</v>
+        <v>3.967999935150146</v>
       </c>
       <c r="I97" t="n">
-        <v>4.199604889512893</v>
+        <v>4.284274263567178</v>
       </c>
       <c r="J97" t="n">
         <v>41</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>60.79999923706055</v>
+        <v>58.70000076293945</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7401315882347959</v>
+        <v>0.7666098707857425</v>
       </c>
       <c r="J99" t="n">
         <v>41</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>5.099999904632568</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="I100" t="n">
-        <v>0.784313740156468</v>
+        <v>0.8080808392180179</v>
       </c>
       <c r="J100" t="n">
         <v>41</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>31.63999938964844</v>
+        <v>31.10000038146973</v>
       </c>
       <c r="I101" t="n">
-        <v>3.318584134813622</v>
+        <v>3.376205746369123</v>
       </c>
       <c r="J101" t="n">
         <v>41</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1.5</v>
+        <v>1.549999952316284</v>
       </c>
       <c r="I102" t="n">
-        <v>3.333333333333333</v>
+        <v>3.225806550850609</v>
       </c>
       <c r="J102" t="n">
         <v>41</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>18.1299991607666</v>
+        <v>18.04999923706055</v>
       </c>
       <c r="I103" t="n">
-        <v>2.095973621567075</v>
+        <v>2.105263246880243</v>
       </c>
       <c r="J103" t="n">
         <v>41</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>25.47999954223633</v>
+        <v>25.31999969482422</v>
       </c>
       <c r="I104" t="n">
-        <v>2.354788111378981</v>
+        <v>2.369668275006531</v>
       </c>
       <c r="J104" t="n">
         <v>41</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>31</v>
+        <v>30.04999923706055</v>
       </c>
       <c r="I105" t="n">
-        <v>1.129032258064516</v>
+        <v>1.164725487141931</v>
       </c>
       <c r="J105" t="n">
         <v>41</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>3.065000057220459</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="I106" t="n">
-        <v>0.5546492555506412</v>
+        <v>0.5821917656103744</v>
       </c>
       <c r="J106" t="n">
         <v>41</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>2.809999942779541</v>
+        <v>2.829999923706055</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3558718933676701</v>
+        <v>0.3533568999855096</v>
       </c>
       <c r="J107" t="n">
         <v>41</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>20.65999984741211</v>
+        <v>20.6299991607666</v>
       </c>
       <c r="I108" t="n">
-        <v>5.42110362183905</v>
+        <v>5.428987133116206</v>
       </c>
       <c r="J108" t="n">
         <v>41</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>1.25</v>
+        <v>1.279999971389771</v>
       </c>
       <c r="I109" t="n">
-        <v>8</v>
+        <v>7.812500174622987</v>
       </c>
       <c r="J109" t="n">
         <v>41</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>2.395999908447266</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="I110" t="n">
-        <v>10.8514194463594</v>
+        <v>10.92436922260721</v>
       </c>
       <c r="J110" t="n">
         <v>41</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>2.053999900817871</v>
+        <v>2.03600001335144</v>
       </c>
       <c r="I111" t="n">
-        <v>4.493671103063225</v>
+        <v>4.533398791489486</v>
       </c>
       <c r="J111" t="n">
         <v>41</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>9.260000228881836</v>
+        <v>8.880000114440918</v>
       </c>
       <c r="I112" t="n">
-        <v>3.779697530766295</v>
+        <v>3.941441390646152</v>
       </c>
       <c r="J112" t="n">
         <v>34</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>4.699999809265137</v>
+        <v>4.440000057220459</v>
       </c>
       <c r="I113" t="n">
-        <v>2.042553274380025</v>
+        <v>2.162162134297318</v>
       </c>
       <c r="J113" t="n">
         <v>34</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>5.800000190734863</v>
+        <v>6</v>
       </c>
       <c r="I114" t="n">
-        <v>5.172413623006964</v>
+        <v>5</v>
       </c>
       <c r="J114" t="n">
         <v>34</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>11.80000019073486</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="I115" t="n">
-        <v>1.694915226840727</v>
+        <v>1.724137874335655</v>
       </c>
       <c r="J115" t="n">
         <v>34</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>9</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I116" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.674157332266361</v>
       </c>
       <c r="J116" t="n">
         <v>34</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>2.140000104904175</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I117" t="n">
-        <v>2.803738180315963</v>
+        <v>2.752293493699352</v>
       </c>
       <c r="J117" t="n">
         <v>34</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>15.31999969482422</v>
+        <v>15.4399995803833</v>
       </c>
       <c r="I118" t="n">
-        <v>3.263707636814917</v>
+        <v>3.238342056921141</v>
       </c>
       <c r="J118" t="n">
         <v>34</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>3.880000114440918</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="I119" t="n">
-        <v>2.577319511610616</v>
+        <v>2.512562802029314</v>
       </c>
       <c r="J119" t="n">
         <v>34</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.46999979019165</v>
+        <v>4.489999771118164</v>
       </c>
       <c r="I121" t="n">
-        <v>2.125279741812402</v>
+        <v>2.115813025450149</v>
       </c>
       <c r="J121" t="n">
         <v>34</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="I123" t="n">
-        <v>1.161290322580645</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>34</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>7</v>
+        <v>6.920000076293945</v>
       </c>
       <c r="I125" t="n">
-        <v>3.142857142857143</v>
+        <v>3.179190716394075</v>
       </c>
       <c r="J125" t="n">
         <v>34</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>3.529999971389771</v>
+        <v>3.545000076293945</v>
       </c>
       <c r="I126" t="n">
-        <v>4.532577940418723</v>
+        <v>4.513399056602251</v>
       </c>
       <c r="J126" t="n">
         <v>27</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>22.70000076293945</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="I127" t="n">
-        <v>2.687224579286799</v>
+        <v>2.735426102554462</v>
       </c>
       <c r="J127" t="n">
         <v>27</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>3.079999923706055</v>
+        <v>3.119999885559082</v>
       </c>
       <c r="I128" t="n">
-        <v>4.870129990766698</v>
+        <v>4.807692484037417</v>
       </c>
       <c r="J128" t="n">
         <v>27</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>11.69999980926514</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="I129" t="n">
-        <v>5.982906080440066</v>
+        <v>5.907172805619612</v>
       </c>
       <c r="J129" t="n">
         <v>27</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>8.840000152587891</v>
+        <v>8.760000228881836</v>
       </c>
       <c r="I130" t="n">
-        <v>5.774886778147308</v>
+        <v>5.827625418511689</v>
       </c>
       <c r="J130" t="n">
         <v>27</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>8.194999694824219</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I131" t="n">
-        <v>3.294692007987823</v>
+        <v>3.292683003418225</v>
       </c>
       <c r="J131" t="n">
         <v>27</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>5.130000114440918</v>
+        <v>5.050000190734863</v>
       </c>
       <c r="I132" t="n">
-        <v>6.822611933569986</v>
+        <v>6.930692807539654</v>
       </c>
       <c r="J132" t="n">
         <v>27</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>10.55000019073486</v>
+        <v>10.25</v>
       </c>
       <c r="I135" t="n">
-        <v>4.075829310198792</v>
+        <v>4.195121951219512</v>
       </c>
       <c r="J135" t="n">
         <v>27</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>12.53999996185303</v>
+        <v>11.96000003814697</v>
       </c>
       <c r="I137" t="n">
-        <v>1.572320578945715</v>
+        <v>1.648570228855522</v>
       </c>
       <c r="J137" t="n">
         <v>27</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>27.25</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="I138" t="n">
-        <v>4.036697247706423</v>
+        <v>4.029304141908979</v>
       </c>
       <c r="J138" t="n">
         <v>27</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>18.79999923706055</v>
+        <v>18.65999984741211</v>
       </c>
       <c r="I139" t="n">
-        <v>2.659574576015658</v>
+        <v>2.679528424912304</v>
       </c>
       <c r="J139" t="n">
         <v>27</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>40.70000076293945</v>
+        <v>41.15000152587891</v>
       </c>
       <c r="I140" t="n">
-        <v>1.154791133144085</v>
+        <v>1.142162776602622</v>
       </c>
       <c r="J140" t="n">
         <v>27</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>2.5</v>
+        <v>2.490000009536743</v>
       </c>
       <c r="I141" t="n">
-        <v>4.399999999999999</v>
+        <v>4.417670665811169</v>
       </c>
       <c r="J141" t="n">
         <v>27</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>78.09999847412109</v>
+        <v>78.30000305175781</v>
       </c>
       <c r="I142" t="n">
-        <v>1.536491707355958</v>
+        <v>1.532566990076331</v>
       </c>
       <c r="J142" t="n">
         <v>27</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>23.39999961853027</v>
+        <v>23.25</v>
       </c>
       <c r="I143" t="n">
-        <v>1.153846172656299</v>
+        <v>1.161290322580645</v>
       </c>
       <c r="J143" t="n">
         <v>27</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>10.19999980926514</v>
+        <v>10.39999961853027</v>
       </c>
       <c r="I144" t="n">
-        <v>3.725490265743223</v>
+        <v>3.653846287868437</v>
       </c>
       <c r="J144" t="n">
         <v>27</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>27</v>
+        <v>27.64999961853027</v>
       </c>
       <c r="I145" t="n">
-        <v>1.111111111111111</v>
+        <v>1.084990973377621</v>
       </c>
       <c r="J145" t="n">
         <v>27</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>0.1508000046014786</v>
+        <v>0.1501999944448471</v>
       </c>
       <c r="I146" t="n">
-        <v>4.64190967268138</v>
+        <v>4.660452902060775</v>
       </c>
       <c r="J146" t="n">
         <v>20</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.820000171661377</v>
+        <v>6.690000057220459</v>
       </c>
       <c r="I147" t="n">
-        <v>2.346040996667943</v>
+        <v>2.391629277002971</v>
       </c>
       <c r="J147" t="n">
         <v>20</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>2.220000028610229</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="I148" t="n">
-        <v>2.927927890194284</v>
+        <v>2.968036452131321</v>
       </c>
       <c r="J148" t="n">
         <v>20</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>7.489999771118164</v>
+        <v>7.559999942779541</v>
       </c>
       <c r="I149" t="n">
-        <v>3.337783813612562</v>
+        <v>3.306878331907552</v>
       </c>
       <c r="J149" t="n">
         <v>20</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>6.659999847412109</v>
+        <v>6.619999885559082</v>
       </c>
       <c r="I151" t="n">
-        <v>7.507507679512727</v>
+        <v>7.552870221202024</v>
       </c>
       <c r="J151" t="n">
         <v>13</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>17.79999923706055</v>
+        <v>17.73999977111816</v>
       </c>
       <c r="I152" t="n">
-        <v>3.651685549776122</v>
+        <v>3.664036123936376</v>
       </c>
       <c r="J152" t="n">
         <v>13</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>12.10499954223633</v>
+        <v>12.06999969482422</v>
       </c>
       <c r="I153" t="n">
-        <v>4.460966711447212</v>
+        <v>4.473902350068488</v>
       </c>
       <c r="J153" t="n">
         <v>13</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>6.296000003814697</v>
+        <v>6.23199987411499</v>
       </c>
       <c r="I154" t="n">
-        <v>1.588310037157096</v>
+        <v>1.604621341783982</v>
       </c>
       <c r="J154" t="n">
         <v>13</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>8.279999732971191</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I155" t="n">
-        <v>1.932367212077019</v>
+        <v>1.975308548948097</v>
       </c>
       <c r="J155" t="n">
         <v>13</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>293.3500061035156</v>
+        <v>286.75</v>
       </c>
       <c r="I156" t="n">
-        <v>1.232316320022288</v>
+        <v>1.260680034873583</v>
       </c>
       <c r="J156" t="n">
         <v>13</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>27.29999923706055</v>
+        <v>27.39999961853027</v>
       </c>
       <c r="I157" t="n">
-        <v>4.981685120905646</v>
+        <v>4.96350371873819</v>
       </c>
       <c r="J157" t="n">
         <v>13</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>13.92000007629395</v>
+        <v>13.55000019073486</v>
       </c>
       <c r="I158" t="n">
-        <v>4.202586183862652</v>
+        <v>4.317343112659199</v>
       </c>
       <c r="J158" t="n">
         <v>13</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>16.57500076293945</v>
+        <v>16.5049991607666</v>
       </c>
       <c r="I159" t="n">
-        <v>3.800904802421706</v>
+        <v>3.817025337980924</v>
       </c>
       <c r="J159" t="n">
         <v>13</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>104.5999984741211</v>
+        <v>104.75</v>
       </c>
       <c r="I160" t="n">
-        <v>0.860420662647206</v>
+        <v>0.8591885441527447</v>
       </c>
       <c r="J160" t="n">
         <v>13</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>62.77000045776367</v>
+        <v>62.40000152587891</v>
       </c>
       <c r="I161" t="n">
-        <v>2.741436972201207</v>
+        <v>2.757692240257942</v>
       </c>
       <c r="J161" t="n">
         <v>13</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>22.89999961853027</v>
+        <v>23</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6113537219743641</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="J162" t="n">
         <v>6</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>1.5</v>
+        <v>1.509999990463257</v>
       </c>
       <c r="I163" t="n">
-        <v>4</v>
+        <v>3.973509958870426</v>
       </c>
       <c r="J163" t="n">
         <v>6</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>1.889999985694885</v>
+        <v>1.879999995231628</v>
       </c>
       <c r="I164" t="n">
-        <v>1.798941812557709</v>
+        <v>1.808510642884921</v>
       </c>
       <c r="J164" t="n">
         <v>-8</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>24.86499977111816</v>
+        <v>24.88500022888184</v>
       </c>
       <c r="I165" t="n">
-        <v>1.045646500676835</v>
+        <v>1.044806098487557</v>
       </c>
       <c r="J165" t="n">
         <v>-15</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>30.15500068664551</v>
+        <v>30.29999923706055</v>
       </c>
       <c r="I166" t="n">
-        <v>0.2984579603735759</v>
+        <v>0.2970297104493625</v>
       </c>
       <c r="J166" t="n">
         <v>-15</v>
@@ -8549,7 +8549,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8559,14 +8559,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8617,7 +8617,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8736,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8770,7 +8770,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8780,14 +8780,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8797,14 +8797,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8814,14 +8814,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8831,14 +8831,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8848,14 +8848,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8872,7 +8872,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8882,14 +8882,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8899,14 +8899,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8923,7 +8923,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8940,7 +8940,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8950,53 +8950,53 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -9008,29 +9008,29 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -9042,34 +9042,34 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9110,7 +9110,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9127,7 +9127,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9137,14 +9137,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9161,7 +9161,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9171,14 +9171,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9188,14 +9188,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9212,7 +9212,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9229,12 +9229,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -9246,12 +9246,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9263,12 +9263,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9280,12 +9280,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -9297,29 +9297,29 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9331,12 +9331,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9348,46 +9348,46 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9399,12 +9399,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9416,12 +9416,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9433,12 +9433,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9450,80 +9450,80 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -9535,12 +9535,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -9552,29 +9552,29 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -9586,29 +9586,29 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9620,24 +9620,24 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9654,63 +9654,63 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9722,63 +9722,63 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9790,12 +9790,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9807,24 +9807,24 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9834,14 +9834,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9851,14 +9851,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9875,7 +9875,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9885,14 +9885,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9902,14 +9902,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9926,7 +9926,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9943,7 +9943,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9977,7 +9977,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9994,7 +9994,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10011,12 +10011,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10028,12 +10028,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -10045,12 +10045,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -10062,12 +10062,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -10079,29 +10079,29 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -10113,12 +10113,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10130,12 +10130,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -10147,7 +10147,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10157,14 +10157,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10181,7 +10181,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10215,7 +10215,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10232,7 +10232,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10249,7 +10249,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10266,7 +10266,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10283,7 +10283,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10300,7 +10300,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10317,7 +10317,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10334,7 +10334,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10351,12 +10351,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -10368,12 +10368,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -10385,12 +10385,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -10402,29 +10402,29 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -10436,12 +10436,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -10453,12 +10453,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -10470,12 +10470,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -10487,12 +10487,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -10504,12 +10504,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -10521,7 +10521,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -10548,14 +10548,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10572,7 +10572,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10589,7 +10589,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10599,14 +10599,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10623,7 +10623,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10633,14 +10633,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10657,7 +10657,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10667,14 +10667,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10684,19 +10684,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10708,17 +10708,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -10730,41 +10730,41 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10776,12 +10776,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -10793,12 +10793,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10810,12 +10810,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10827,29 +10827,29 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10861,7 +10861,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10878,7 +10878,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10895,7 +10895,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10912,7 +10912,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10929,7 +10929,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10946,7 +10946,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10963,7 +10963,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10980,7 +10980,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10997,7 +10997,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11014,7 +11014,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11031,7 +11031,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11082,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11092,14 +11092,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11109,14 +11109,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11133,7 +11133,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11150,7 +11150,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11167,7 +11167,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11184,7 +11184,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11194,14 +11194,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11218,7 +11218,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11235,63 +11235,63 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11303,12 +11303,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11320,12 +11320,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11337,12 +11337,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11354,29 +11354,29 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11388,12 +11388,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11405,7 +11405,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11422,7 +11422,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11439,7 +11439,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11456,7 +11456,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11466,14 +11466,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11490,7 +11490,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11507,7 +11507,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11524,7 +11524,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11541,7 +11541,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11558,7 +11558,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11575,7 +11575,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11585,14 +11585,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11602,14 +11602,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11626,7 +11626,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -11643,7 +11643,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -11660,7 +11660,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -11677,7 +11677,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -11694,7 +11694,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -11711,7 +11711,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -11728,7 +11728,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -11745,7 +11745,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -11762,7 +11762,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -11772,14 +11772,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -11796,7 +11796,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -11813,7 +11813,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -11830,7 +11830,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -11847,7 +11847,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -11864,7 +11864,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -11881,7 +11881,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -11898,7 +11898,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -11915,7 +11915,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -11932,7 +11932,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -11949,7 +11949,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -11959,14 +11959,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -11976,14 +11976,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -11993,14 +11993,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12017,7 +12017,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12034,7 +12034,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12051,7 +12051,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12061,14 +12061,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12085,7 +12085,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12102,7 +12102,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12112,14 +12112,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12136,7 +12136,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12153,7 +12153,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12170,7 +12170,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12187,7 +12187,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12204,7 +12204,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12221,29 +12221,29 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -12255,29 +12255,29 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -12289,12 +12289,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -12306,12 +12306,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -12323,29 +12323,29 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -12357,29 +12357,29 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -12391,7 +12391,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12408,7 +12408,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12425,7 +12425,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12442,7 +12442,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12459,7 +12459,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12476,7 +12476,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12493,7 +12493,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12510,7 +12510,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12527,7 +12527,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -12544,7 +12544,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -12561,7 +12561,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -12578,7 +12578,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -12595,7 +12595,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -12605,14 +12605,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -12629,7 +12629,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -12646,7 +12646,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -12663,7 +12663,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -12680,7 +12680,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -12690,14 +12690,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -12714,7 +12714,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -12731,7 +12731,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -12748,7 +12748,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -12765,7 +12765,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -12775,14 +12775,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -12792,14 +12792,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -12816,7 +12816,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -12833,7 +12833,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -12843,14 +12843,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -12867,7 +12867,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -12884,7 +12884,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -12901,7 +12901,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -12918,7 +12918,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -12928,14 +12928,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -12952,7 +12952,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -12962,14 +12962,14 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -12979,14 +12979,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -12996,14 +12996,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13013,14 +13013,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13037,7 +13037,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13054,7 +13054,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13064,14 +13064,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13088,7 +13088,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13105,7 +13105,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13115,14 +13115,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13139,7 +13139,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13156,7 +13156,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13173,7 +13173,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13190,7 +13190,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13207,7 +13207,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13224,7 +13224,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13241,7 +13241,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13258,7 +13258,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13268,14 +13268,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13292,7 +13292,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13309,7 +13309,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13326,7 +13326,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13343,7 +13343,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13360,7 +13360,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13377,7 +13377,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13394,7 +13394,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13411,7 +13411,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13428,7 +13428,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -13438,14 +13438,14 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -13455,14 +13455,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13479,7 +13479,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -13489,14 +13489,14 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -13506,14 +13506,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -13523,14 +13523,14 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -13547,7 +13547,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -13564,7 +13564,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -13581,7 +13581,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -13598,7 +13598,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -13615,7 +13615,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -13632,7 +13632,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -13642,14 +13642,14 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -13666,7 +13666,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -13683,7 +13683,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -13700,7 +13700,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -13717,29 +13717,29 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -13751,12 +13751,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -13768,7 +13768,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -13785,7 +13785,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -13802,7 +13802,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -13812,14 +13812,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -13829,14 +13829,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -13853,7 +13853,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -13870,7 +13870,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -13904,7 +13904,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -13921,7 +13921,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -13938,7 +13938,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -13955,7 +13955,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -13965,14 +13965,14 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -13989,7 +13989,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14006,7 +14006,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14016,14 +14016,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14040,7 +14040,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14057,7 +14057,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14074,7 +14074,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14091,7 +14091,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14101,14 +14101,14 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14125,7 +14125,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14142,7 +14142,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14159,7 +14159,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -14169,14 +14169,14 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14193,7 +14193,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14210,7 +14210,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14227,7 +14227,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14244,7 +14244,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14261,7 +14261,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14278,7 +14278,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14295,7 +14295,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14312,7 +14312,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14329,7 +14329,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14346,7 +14346,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14363,7 +14363,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14373,14 +14373,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14390,14 +14390,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14414,7 +14414,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14431,7 +14431,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14448,7 +14448,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -14465,7 +14465,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14475,14 +14475,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -14499,7 +14499,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -14516,7 +14516,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -14526,14 +14526,14 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -14550,7 +14550,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -14567,7 +14567,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -14584,7 +14584,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -14601,7 +14601,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -14618,7 +14618,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -14635,7 +14635,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -14652,7 +14652,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -14669,7 +14669,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -14686,7 +14686,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -14703,7 +14703,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -14720,7 +14720,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -14737,7 +14737,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -14754,7 +14754,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -14764,14 +14764,14 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -14781,14 +14781,14 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -14805,46 +14805,46 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -14856,29 +14856,29 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -14890,12 +14890,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -14907,12 +14907,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -14924,29 +14924,29 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -14958,12 +14958,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -14975,7 +14975,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -14992,7 +14992,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15009,7 +15009,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15026,7 +15026,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15043,7 +15043,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15060,7 +15060,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15070,14 +15070,14 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15094,7 +15094,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15111,7 +15111,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15121,36 +15121,36 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -15162,12 +15162,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -15179,29 +15179,29 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -15213,46 +15213,46 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -15264,41 +15264,41 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15308,14 +15308,14 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15325,14 +15325,14 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -15342,14 +15342,14 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15366,7 +15366,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -15376,14 +15376,14 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -15393,14 +15393,14 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -15410,14 +15410,14 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -15434,7 +15434,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -15444,14 +15444,14 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -15461,14 +15461,14 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -15478,14 +15478,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -15495,14 +15495,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -15519,7 +15519,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -15536,7 +15536,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -15546,14 +15546,14 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -15570,7 +15570,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -15580,70 +15580,70 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -15655,46 +15655,46 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -15706,29 +15706,29 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -15740,12 +15740,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -15767,14 +15767,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -15791,7 +15791,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -15808,7 +15808,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -15818,14 +15818,14 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -15835,14 +15835,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -15859,7 +15859,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -15869,14 +15869,14 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -15886,14 +15886,14 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -15903,14 +15903,14 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -15927,7 +15927,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -15944,7 +15944,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -15954,14 +15954,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -15971,14 +15971,14 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -15988,14 +15988,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16012,7 +16012,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16029,7 +16029,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16039,14 +16039,14 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -16056,14 +16056,14 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -16073,14 +16073,14 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16097,7 +16097,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16114,7 +16114,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -16124,14 +16124,14 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16141,14 +16141,14 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -16158,14 +16158,14 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -16175,14 +16175,14 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -16192,14 +16192,14 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -16216,7 +16216,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -16233,7 +16233,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -16250,7 +16250,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -16260,14 +16260,14 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16277,14 +16277,14 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16294,14 +16294,14 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16311,14 +16311,14 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16335,7 +16335,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -16352,7 +16352,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16369,7 +16369,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -16379,14 +16379,14 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -16403,7 +16403,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16413,14 +16413,14 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -16430,14 +16430,14 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -16464,14 +16464,14 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -16488,7 +16488,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -16505,7 +16505,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -16522,7 +16522,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -16532,14 +16532,14 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -16549,14 +16549,14 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -16566,14 +16566,14 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -16583,14 +16583,14 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -16600,14 +16600,14 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -16617,14 +16617,14 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -16634,14 +16634,14 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -16651,14 +16651,14 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -16675,7 +16675,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -16692,7 +16692,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -16702,14 +16702,14 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -16726,7 +16726,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -16736,14 +16736,14 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -16760,7 +16760,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -16798,843 +16798,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BANCA IFIS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BANCA IFIS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BREMBO N.V.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Banca Profilo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CALTAGIRONE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Cementir Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CleanBnB S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Comer Industries S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Dexelance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Dexelance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Directa SIM S.P.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ENEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ENEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Estrima S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>FinecoBank S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Homizy SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>IGD SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>INTERCOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>INTERCOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Iveco Group N.V.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Leonardo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Matica Fintec S.p.A.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Nexi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Poste Italiane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>RCS MediaGroup S.p.A.</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SAFILO GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>TELECOM ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>TERNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>TERNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>iVision Tech S.p.A.</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>